--- a/excel_reports/backtest_compare/s13/compare_s13_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s13/compare_s13_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 15:04:48</t>
+          <t>2026-06-18 17:39:19</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -1197,10 +1197,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46170.625</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4394.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46170.67708333334</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4395.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE4" s="9" t="n">
-        <v>46170.67708333334</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF4" s="8" t="n">
-        <v>4398.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG4" s="8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI4" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="8" t="inlineStr"/>
       <c r="AK4" s="8" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
       <c r="AM4" s="8" t="inlineStr"/>
       <c r="AN4" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO4" s="8" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>46170.75</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>4383.06</v>
+        <v>4392.68</v>
       </c>
       <c r="AG5" s="8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>-9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="8" t="inlineStr"/>
       <c r="AK5" s="8" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       <c r="AM5" s="8" t="inlineStr"/>
       <c r="AN5" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO5" s="8" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>46170.84375</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>4434.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG10" s="8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="8" t="inlineStr"/>
       <c r="AK10" s="8" t="inlineStr"/>
@@ -1947,7 +1947,7 @@
       <c r="AM10" s="8" t="inlineStr"/>
       <c r="AN10" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO10" s="8" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>46170.875</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>4435.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG11" s="8" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="8" t="inlineStr"/>
       <c r="AK11" s="8" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
       <c r="AM11" s="8" t="inlineStr"/>
       <c r="AN11" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO11" s="8" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>46170.875</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>4438.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG12" s="8" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI12" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="8" t="inlineStr"/>
       <c r="AK12" s="8" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       <c r="AM12" s="8" t="inlineStr"/>
       <c r="AN12" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO12" s="8" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>46171.42708333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF13" s="8" t="n">
-        <v>4496.39</v>
+        <v>4432.15</v>
       </c>
       <c r="AG13" s="8" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>64.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="8" t="inlineStr"/>
       <c r="AK13" s="8" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       <c r="AM13" s="8" t="inlineStr"/>
       <c r="AN13" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO13" s="8" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG14" s="8" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI14" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="8" t="inlineStr"/>
       <c r="AK14" s="8" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       <c r="AM14" s="8" t="inlineStr"/>
       <c r="AN14" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO14" s="8" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF15" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG15" s="8" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI15" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="8" t="inlineStr"/>
       <c r="AK15" s="8" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       <c r="AM15" s="8" t="inlineStr"/>
       <c r="AN15" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO15" s="8" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI16" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="8" t="inlineStr"/>
       <c r="AK16" s="8" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       <c r="AM16" s="8" t="inlineStr"/>
       <c r="AN16" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO16" s="8" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI17" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="8" t="inlineStr"/>
       <c r="AK17" s="8" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
       <c r="AM17" s="8" t="inlineStr"/>
       <c r="AN17" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO17" s="8" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE22" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF22" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG22" s="8" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI22" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="8" t="inlineStr"/>
       <c r="AK22" s="8" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="AM22" s="8" t="inlineStr"/>
       <c r="AN22" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO22" s="8" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE23" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG23" s="8" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI23" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ23" s="8" t="inlineStr"/>
       <c r="AK23" s="8" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
       <c r="AM23" s="8" t="inlineStr"/>
       <c r="AN23" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO23" s="8" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE24" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG24" s="8" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI24" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="8" t="inlineStr"/>
       <c r="AK24" s="8" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       <c r="AM24" s="8" t="inlineStr"/>
       <c r="AN24" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO24" s="8" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE25" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG25" s="8" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI25" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ25" s="8" t="inlineStr"/>
       <c r="AK25" s="8" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="AM25" s="8" t="inlineStr"/>
       <c r="AN25" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO25" s="8" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE30" s="9" t="n">
-        <v>46172.07291666666</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF30" s="8" t="n">
-        <v>4552.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG30" s="8" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI30" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="8" t="inlineStr"/>
       <c r="AK30" s="8" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
       <c r="AM30" s="8" t="inlineStr"/>
       <c r="AN30" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO30" s="8" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE31" s="9" t="n">
-        <v>46172.07291666666</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF31" s="8" t="n">
-        <v>4551.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG31" s="8" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI31" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="8" t="inlineStr"/>
       <c r="AK31" s="8" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       <c r="AM31" s="8" t="inlineStr"/>
       <c r="AN31" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO31" s="8" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE32" s="9" t="n">
-        <v>46172.11458333334</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF32" s="8" t="n">
-        <v>4548.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG32" s="8" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI32" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="8" t="inlineStr"/>
       <c r="AK32" s="8" t="inlineStr"/>
@@ -3949,7 +3949,7 @@
       <c r="AM32" s="8" t="inlineStr"/>
       <c r="AN32" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO32" s="8" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE33" s="9" t="n">
-        <v>46174.84375</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF33" s="8" t="n">
-        <v>4470.65</v>
+        <v>4554.13</v>
       </c>
       <c r="AG33" s="8" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI33" s="8" t="n">
-        <v>83.48</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="8" t="inlineStr"/>
       <c r="AK33" s="8" t="inlineStr"/>
@@ -4040,7 +4040,7 @@
       <c r="AM33" s="8" t="inlineStr"/>
       <c r="AN33" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO33" s="8" t="inlineStr"/>
@@ -4109,10 +4109,10 @@
         <v>46175</v>
       </c>
       <c r="AE34" s="9" t="n">
-        <v>46175.01041666666</v>
+        <v>46175</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>4482.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG34" s="8" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI34" s="8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AJ34" s="8" t="inlineStr"/>
       <c r="AK34" s="8" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       <c r="AM34" s="8" t="inlineStr"/>
       <c r="AN34" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO34" s="8" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         <v>46175</v>
       </c>
       <c r="AE35" s="9" t="n">
-        <v>46175.02083333334</v>
+        <v>46175</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>4483.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG35" s="8" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI35" s="8" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="8" t="inlineStr"/>
       <c r="AK35" s="8" t="inlineStr"/>
@@ -4222,7 +4222,7 @@
       <c r="AM35" s="8" t="inlineStr"/>
       <c r="AN35" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO35" s="8" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         <v>46175</v>
       </c>
       <c r="AE36" s="9" t="n">
-        <v>46175.02083333334</v>
+        <v>46175</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>4486.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG36" s="8" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI36" s="8" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="8" t="inlineStr"/>
       <c r="AK36" s="8" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
       <c r="AM36" s="8" t="inlineStr"/>
       <c r="AN36" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO36" s="8" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         <v>46175</v>
       </c>
       <c r="AE37" s="9" t="n">
-        <v>46175.36458333334</v>
+        <v>46175</v>
       </c>
       <c r="AF37" s="8" t="n">
-        <v>4479.85</v>
+        <v>4480.07</v>
       </c>
       <c r="AG37" s="8" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI37" s="8" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="8" t="inlineStr"/>
       <c r="AK37" s="8" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       <c r="AM37" s="8" t="inlineStr"/>
       <c r="AN37" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO37" s="8" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE38" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>4477.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG38" s="8" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI38" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="8" t="inlineStr"/>
       <c r="AK38" s="8" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="AM38" s="8" t="inlineStr"/>
       <c r="AN38" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO38" s="8" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE39" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF39" s="8" t="n">
-        <v>4476.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG39" s="8" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI39" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ39" s="8" t="inlineStr"/>
       <c r="AK39" s="8" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
       <c r="AM39" s="8" t="inlineStr"/>
       <c r="AN39" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO39" s="8" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE40" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF40" s="8" t="n">
-        <v>4473.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG40" s="8" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI40" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ40" s="8" t="inlineStr"/>
       <c r="AK40" s="8" t="inlineStr"/>
@@ -4677,7 +4677,7 @@
       <c r="AM40" s="8" t="inlineStr"/>
       <c r="AN40" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO40" s="8" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE41" s="9" t="n">
-        <v>46175.4375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF41" s="8" t="n">
-        <v>4495.18</v>
+        <v>4479.85</v>
       </c>
       <c r="AG41" s="8" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI41" s="8" t="n">
-        <v>-15.33</v>
+        <v>0</v>
       </c>
       <c r="AJ41" s="8" t="inlineStr"/>
       <c r="AK41" s="8" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       <c r="AM41" s="8" t="inlineStr"/>
       <c r="AN41" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO41" s="8" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE46" s="9" t="n">
-        <v>46175.84375</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF46" s="8" t="n">
-        <v>4512.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG46" s="8" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI46" s="8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AJ46" s="8" t="inlineStr"/>
       <c r="AK46" s="8" t="inlineStr"/>
@@ -5223,7 +5223,7 @@
       <c r="AM46" s="8" t="inlineStr"/>
       <c r="AN46" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO46" s="8" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE47" s="9" t="n">
-        <v>46175.84375</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF47" s="8" t="n">
-        <v>4511.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG47" s="8" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI47" s="8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AJ47" s="8" t="inlineStr"/>
       <c r="AK47" s="8" t="inlineStr"/>
@@ -5314,7 +5314,7 @@
       <c r="AM47" s="8" t="inlineStr"/>
       <c r="AN47" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO47" s="8" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE48" s="9" t="n">
-        <v>46175.85416666666</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF48" s="8" t="n">
-        <v>4508.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG48" s="8" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI48" s="8" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="AJ48" s="8" t="inlineStr"/>
       <c r="AK48" s="8" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
       <c r="AM48" s="8" t="inlineStr"/>
       <c r="AN48" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO48" s="8" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE49" s="9" t="n">
-        <v>46176.3125</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF49" s="8" t="n">
-        <v>4483.45</v>
+        <v>4514.66</v>
       </c>
       <c r="AG49" s="8" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI49" s="8" t="n">
-        <v>31.21</v>
+        <v>0</v>
       </c>
       <c r="AJ49" s="8" t="inlineStr"/>
       <c r="AK49" s="8" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
       <c r="AM49" s="8" t="inlineStr"/>
       <c r="AN49" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO49" s="8" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE50" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF50" s="8" t="n">
-        <v>4485.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG50" s="8" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI50" s="8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="8" t="inlineStr"/>
       <c r="AK50" s="8" t="inlineStr"/>
@@ -5587,7 +5587,7 @@
       <c r="AM50" s="8" t="inlineStr"/>
       <c r="AN50" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO50" s="8" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE51" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF51" s="8" t="n">
-        <v>4486.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG51" s="8" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI51" s="8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="8" t="inlineStr"/>
       <c r="AK51" s="8" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
       <c r="AM51" s="8" t="inlineStr"/>
       <c r="AN51" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO51" s="8" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE52" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF52" s="8" t="n">
-        <v>4489.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG52" s="8" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI52" s="8" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="8" t="inlineStr"/>
       <c r="AK52" s="8" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
       <c r="AM52" s="8" t="inlineStr"/>
       <c r="AN52" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO52" s="8" t="inlineStr"/>
@@ -5838,10 +5838,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE53" s="9" t="n">
-        <v>46176.34375</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF53" s="8" t="n">
-        <v>4471.34</v>
+        <v>4483.45</v>
       </c>
       <c r="AG53" s="8" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI53" s="8" t="n">
-        <v>-12.11</v>
+        <v>0</v>
       </c>
       <c r="AJ53" s="8" t="inlineStr"/>
       <c r="AK53" s="8" t="inlineStr"/>
@@ -5860,7 +5860,7 @@
       <c r="AM53" s="8" t="inlineStr"/>
       <c r="AN53" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO53" s="8" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE62" s="9" t="n">
-        <v>46176.51041666666</v>
+        <v>46176.5</v>
       </c>
       <c r="AF62" s="8" t="n">
-        <v>4467.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG62" s="8" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI62" s="8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AJ62" s="8" t="inlineStr"/>
       <c r="AK62" s="8" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       <c r="AM62" s="8" t="inlineStr"/>
       <c r="AN62" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO62" s="8" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE63" s="9" t="n">
-        <v>46176.51041666666</v>
+        <v>46176.5</v>
       </c>
       <c r="AF63" s="8" t="n">
-        <v>4466.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG63" s="8" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI63" s="8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AJ63" s="8" t="inlineStr"/>
       <c r="AK63" s="8" t="inlineStr"/>
@@ -6770,7 +6770,7 @@
       <c r="AM63" s="8" t="inlineStr"/>
       <c r="AN63" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO63" s="8" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE64" s="9" t="n">
-        <v>46176.52083333334</v>
+        <v>46176.5</v>
       </c>
       <c r="AF64" s="8" t="n">
-        <v>4463.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG64" s="8" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI64" s="8" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AJ64" s="8" t="inlineStr"/>
       <c r="AK64" s="8" t="inlineStr"/>
@@ -6861,7 +6861,7 @@
       <c r="AM64" s="8" t="inlineStr"/>
       <c r="AN64" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO64" s="8" t="inlineStr"/>
@@ -6930,10 +6930,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE65" s="9" t="n">
-        <v>46176.71875</v>
+        <v>46176.5</v>
       </c>
       <c r="AF65" s="8" t="n">
-        <v>4463.07</v>
+        <v>4469.51</v>
       </c>
       <c r="AG65" s="8" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI65" s="8" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="AJ65" s="8" t="inlineStr"/>
       <c r="AK65" s="8" t="inlineStr"/>
@@ -6952,7 +6952,7 @@
       <c r="AM65" s="8" t="inlineStr"/>
       <c r="AN65" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO65" s="8" t="inlineStr"/>
@@ -7021,10 +7021,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE66" s="9" t="n">
-        <v>46176.75</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF66" s="8" t="n">
-        <v>4465.06</v>
+        <v>4463.07</v>
       </c>
       <c r="AG66" s="8" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI66" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ66" s="8" t="inlineStr"/>
       <c r="AK66" s="8" t="inlineStr"/>
@@ -7043,7 +7043,7 @@
       <c r="AM66" s="8" t="inlineStr"/>
       <c r="AN66" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO66" s="8" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE67" s="9" t="n">
-        <v>46176.75</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF67" s="8" t="n">
-        <v>4466.06</v>
+        <v>4463.07</v>
       </c>
       <c r="AG67" s="8" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI67" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ67" s="8" t="inlineStr"/>
       <c r="AK67" s="8" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
       <c r="AM67" s="8" t="inlineStr"/>
       <c r="AN67" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO67" s="8" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE68" s="9" t="n">
-        <v>46176.86458333334</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF68" s="8" t="n">
-        <v>4427.32</v>
+        <v>4463.07</v>
       </c>
       <c r="AG68" s="8" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI68" s="8" t="n">
-        <v>-35.75</v>
+        <v>0</v>
       </c>
       <c r="AJ68" s="8" t="inlineStr"/>
       <c r="AK68" s="8" t="inlineStr"/>
@@ -7225,7 +7225,7 @@
       <c r="AM68" s="8" t="inlineStr"/>
       <c r="AN68" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO68" s="8" t="inlineStr"/>
@@ -7294,10 +7294,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE69" s="9" t="n">
-        <v>46176.86458333334</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF69" s="8" t="n">
-        <v>4427.32</v>
+        <v>4463.07</v>
       </c>
       <c r="AG69" s="8" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI69" s="8" t="n">
-        <v>-35.75</v>
+        <v>0</v>
       </c>
       <c r="AJ69" s="8" t="inlineStr"/>
       <c r="AK69" s="8" t="inlineStr"/>
@@ -7316,7 +7316,7 @@
       <c r="AM69" s="8" t="inlineStr"/>
       <c r="AN69" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO69" s="8" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE74" s="9" t="n">
-        <v>46176.90625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF74" s="8" t="n">
-        <v>4456.54</v>
+        <v>4454.76</v>
       </c>
       <c r="AG74" s="8" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI74" s="8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AJ74" s="8" t="inlineStr"/>
       <c r="AK74" s="8" t="inlineStr"/>
@@ -7771,7 +7771,7 @@
       <c r="AM74" s="8" t="inlineStr"/>
       <c r="AN74" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO74" s="8" t="inlineStr"/>
@@ -7840,10 +7840,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE75" s="9" t="n">
-        <v>46176.90625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF75" s="8" t="n">
-        <v>4457.54</v>
+        <v>4454.76</v>
       </c>
       <c r="AG75" s="8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI75" s="8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AJ75" s="8" t="inlineStr"/>
       <c r="AK75" s="8" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       <c r="AM75" s="8" t="inlineStr"/>
       <c r="AN75" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO75" s="8" t="inlineStr"/>
@@ -7931,10 +7931,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE76" s="9" t="n">
-        <v>46177.15625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF76" s="8" t="n">
-        <v>4433.48</v>
+        <v>4454.76</v>
       </c>
       <c r="AG76" s="8" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI76" s="8" t="n">
-        <v>-21.28</v>
+        <v>0</v>
       </c>
       <c r="AJ76" s="8" t="inlineStr"/>
       <c r="AK76" s="8" t="inlineStr"/>
@@ -7953,7 +7953,7 @@
       <c r="AM76" s="8" t="inlineStr"/>
       <c r="AN76" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO76" s="8" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE77" s="9" t="n">
-        <v>46177.15625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF77" s="8" t="n">
-        <v>4433.48</v>
+        <v>4454.76</v>
       </c>
       <c r="AG77" s="8" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI77" s="8" t="n">
-        <v>-21.28</v>
+        <v>0</v>
       </c>
       <c r="AJ77" s="8" t="inlineStr"/>
       <c r="AK77" s="8" t="inlineStr"/>
@@ -8044,7 +8044,7 @@
       <c r="AM77" s="8" t="inlineStr"/>
       <c r="AN77" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO77" s="8" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE78" s="9" t="n">
-        <v>46177.20833333334</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF78" s="8" t="n">
-        <v>4431.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG78" s="8" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI78" s="8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ78" s="8" t="inlineStr"/>
       <c r="AK78" s="8" t="inlineStr"/>
@@ -8135,7 +8135,7 @@
       <c r="AM78" s="8" t="inlineStr"/>
       <c r="AN78" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO78" s="8" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE79" s="9" t="n">
-        <v>46177.20833333334</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF79" s="8" t="n">
-        <v>4430.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG79" s="8" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI79" s="8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ79" s="8" t="inlineStr"/>
       <c r="AK79" s="8" t="inlineStr"/>
@@ -8226,7 +8226,7 @@
       <c r="AM79" s="8" t="inlineStr"/>
       <c r="AN79" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO79" s="8" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE80" s="9" t="n">
-        <v>46177.21875</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF80" s="8" t="n">
-        <v>4427.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG80" s="8" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI80" s="8" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="AJ80" s="8" t="inlineStr"/>
       <c r="AK80" s="8" t="inlineStr"/>
@@ -8317,7 +8317,7 @@
       <c r="AM80" s="8" t="inlineStr"/>
       <c r="AN80" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO80" s="8" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE81" s="9" t="n">
-        <v>46177.25</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF81" s="8" t="n">
-        <v>4449.14</v>
+        <v>4433.48</v>
       </c>
       <c r="AG81" s="8" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI81" s="8" t="n">
-        <v>-15.66</v>
+        <v>0</v>
       </c>
       <c r="AJ81" s="8" t="inlineStr"/>
       <c r="AK81" s="8" t="inlineStr"/>
@@ -8408,7 +8408,7 @@
       <c r="AM81" s="8" t="inlineStr"/>
       <c r="AN81" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO81" s="8" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE86" s="9" t="n">
-        <v>46177.60416666666</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF86" s="8" t="n">
-        <v>4462.16</v>
+        <v>4464.11</v>
       </c>
       <c r="AG86" s="8" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI86" s="8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ86" s="8" t="inlineStr"/>
       <c r="AK86" s="8" t="inlineStr"/>
@@ -8863,7 +8863,7 @@
       <c r="AM86" s="8" t="inlineStr"/>
       <c r="AN86" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO86" s="8" t="inlineStr"/>
@@ -8932,10 +8932,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE87" s="9" t="n">
-        <v>46177.60416666666</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF87" s="8" t="n">
-        <v>4461.16</v>
+        <v>4464.11</v>
       </c>
       <c r="AG87" s="8" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI87" s="8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AJ87" s="8" t="inlineStr"/>
       <c r="AK87" s="8" t="inlineStr"/>
@@ -8954,7 +8954,7 @@
       <c r="AM87" s="8" t="inlineStr"/>
       <c r="AN87" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO87" s="8" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE88" s="9" t="n">
-        <v>46177.77083333334</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF88" s="8" t="n">
-        <v>4489.65</v>
+        <v>4464.11</v>
       </c>
       <c r="AG88" s="8" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI88" s="8" t="n">
-        <v>-25.54</v>
+        <v>0</v>
       </c>
       <c r="AJ88" s="8" t="inlineStr"/>
       <c r="AK88" s="8" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
       <c r="AM88" s="8" t="inlineStr"/>
       <c r="AN88" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO88" s="8" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE89" s="9" t="n">
-        <v>46177.77083333334</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF89" s="8" t="n">
-        <v>4489.65</v>
+        <v>4464.11</v>
       </c>
       <c r="AG89" s="8" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI89" s="8" t="n">
-        <v>-25.54</v>
+        <v>0</v>
       </c>
       <c r="AJ89" s="8" t="inlineStr"/>
       <c r="AK89" s="8" t="inlineStr"/>
@@ -9136,7 +9136,7 @@
       <c r="AM89" s="8" t="inlineStr"/>
       <c r="AN89" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO89" s="8" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE94" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF94" s="8" t="n">
-        <v>4485.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG94" s="8" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI94" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ94" s="8" t="inlineStr"/>
       <c r="AK94" s="8" t="inlineStr"/>
@@ -9591,7 +9591,7 @@
       <c r="AM94" s="8" t="inlineStr"/>
       <c r="AN94" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO94" s="8" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE95" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF95" s="8" t="n">
-        <v>4484.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG95" s="8" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI95" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ95" s="8" t="inlineStr"/>
       <c r="AK95" s="8" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       <c r="AM95" s="8" t="inlineStr"/>
       <c r="AN95" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO95" s="8" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE96" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF96" s="8" t="n">
-        <v>4481.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG96" s="8" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI96" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ96" s="8" t="inlineStr"/>
       <c r="AK96" s="8" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       <c r="AM96" s="8" t="inlineStr"/>
       <c r="AN96" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO96" s="8" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE97" s="9" t="n">
-        <v>46178.58333333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF97" s="8" t="n">
-        <v>4452.87</v>
+        <v>4487.82</v>
       </c>
       <c r="AG97" s="8" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI97" s="8" t="n">
-        <v>34.95</v>
+        <v>0</v>
       </c>
       <c r="AJ97" s="8" t="inlineStr"/>
       <c r="AK97" s="8" t="inlineStr"/>
@@ -9864,7 +9864,7 @@
       <c r="AM97" s="8" t="inlineStr"/>
       <c r="AN97" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO97" s="8" t="inlineStr"/>
@@ -9933,10 +9933,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE98" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF98" s="8" t="n">
-        <v>4454.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG98" s="8" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI98" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ98" s="8" t="inlineStr"/>
       <c r="AK98" s="8" t="inlineStr"/>
@@ -9955,7 +9955,7 @@
       <c r="AM98" s="8" t="inlineStr"/>
       <c r="AN98" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO98" s="8" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE99" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF99" s="8" t="n">
-        <v>4455.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG99" s="8" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI99" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ99" s="8" t="inlineStr"/>
       <c r="AK99" s="8" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       <c r="AM99" s="8" t="inlineStr"/>
       <c r="AN99" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO99" s="8" t="inlineStr"/>
@@ -10115,10 +10115,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE100" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF100" s="8" t="n">
-        <v>4458.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG100" s="8" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI100" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ100" s="8" t="inlineStr"/>
       <c r="AK100" s="8" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       <c r="AM100" s="8" t="inlineStr"/>
       <c r="AN100" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO100" s="8" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE101" s="9" t="n">
-        <v>46178.82291666666</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF101" s="8" t="n">
-        <v>4413.06</v>
+        <v>4452.87</v>
       </c>
       <c r="AG101" s="8" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI101" s="8" t="n">
-        <v>-39.81</v>
+        <v>0</v>
       </c>
       <c r="AJ101" s="8" t="inlineStr"/>
       <c r="AK101" s="8" t="inlineStr"/>
@@ -10228,7 +10228,7 @@
       <c r="AM101" s="8" t="inlineStr"/>
       <c r="AN101" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO101" s="8" t="inlineStr"/>
@@ -10661,10 +10661,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE106" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF106" s="8" t="n">
-        <v>4340.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG106" s="8" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI106" s="8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AJ106" s="8" t="inlineStr"/>
       <c r="AK106" s="8" t="inlineStr"/>
@@ -10683,7 +10683,7 @@
       <c r="AM106" s="8" t="inlineStr"/>
       <c r="AN106" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO106" s="8" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE107" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF107" s="8" t="n">
-        <v>4341.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG107" s="8" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI107" s="8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AJ107" s="8" t="inlineStr"/>
       <c r="AK107" s="8" t="inlineStr"/>
@@ -10774,7 +10774,7 @@
       <c r="AM107" s="8" t="inlineStr"/>
       <c r="AN107" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO107" s="8" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE108" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF108" s="8" t="n">
-        <v>4344.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG108" s="8" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI108" s="8" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AJ108" s="8" t="inlineStr"/>
       <c r="AK108" s="8" t="inlineStr"/>
@@ -10865,7 +10865,7 @@
       <c r="AM108" s="8" t="inlineStr"/>
       <c r="AN108" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO108" s="8" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE109" s="9" t="n">
-        <v>46181.34375</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF109" s="8" t="n">
-        <v>4326.96</v>
+        <v>4338.98</v>
       </c>
       <c r="AG109" s="8" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI109" s="8" t="n">
-        <v>-12.02</v>
+        <v>0</v>
       </c>
       <c r="AJ109" s="8" t="inlineStr"/>
       <c r="AK109" s="8" t="inlineStr"/>
@@ -10956,7 +10956,7 @@
       <c r="AM109" s="8" t="inlineStr"/>
       <c r="AN109" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO109" s="8" t="inlineStr"/>
@@ -12325,7 +12325,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -12710,10 +12710,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46170.625</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4394.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -12732,7 +12732,7 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr"/>
@@ -12801,10 +12801,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46170.67708333334</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4395.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -12823,7 +12823,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE4" s="9" t="n">
-        <v>46170.67708333334</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF4" s="8" t="n">
-        <v>4398.67</v>
+        <v>4392.68</v>
       </c>
       <c r="AG4" s="8" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI4" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="8" t="inlineStr"/>
       <c r="AK4" s="8" t="inlineStr"/>
@@ -12914,7 +12914,7 @@
       <c r="AM4" s="8" t="inlineStr"/>
       <c r="AN4" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO4" s="8" t="inlineStr"/>
@@ -12983,10 +12983,10 @@
         <v>46170.60416666666</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>46170.75</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>4383.06</v>
+        <v>4392.68</v>
       </c>
       <c r="AG5" s="8" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>4392.68</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>-9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="8" t="inlineStr"/>
       <c r="AK5" s="8" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
       <c r="AM5" s="8" t="inlineStr"/>
       <c r="AN5" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO5" s="8" t="inlineStr"/>
@@ -13438,10 +13438,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>46170.84375</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>4434.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG10" s="8" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="8" t="inlineStr"/>
       <c r="AK10" s="8" t="inlineStr"/>
@@ -13460,7 +13460,7 @@
       <c r="AM10" s="8" t="inlineStr"/>
       <c r="AN10" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO10" s="8" t="inlineStr"/>
@@ -13529,10 +13529,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>46170.875</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>4435.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG11" s="8" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="8" t="inlineStr"/>
       <c r="AK11" s="8" t="inlineStr"/>
@@ -13551,7 +13551,7 @@
       <c r="AM11" s="8" t="inlineStr"/>
       <c r="AN11" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO11" s="8" t="inlineStr"/>
@@ -13620,10 +13620,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>46170.875</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>4438.14</v>
+        <v>4432.15</v>
       </c>
       <c r="AG12" s="8" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI12" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="8" t="inlineStr"/>
       <c r="AK12" s="8" t="inlineStr"/>
@@ -13642,7 +13642,7 @@
       <c r="AM12" s="8" t="inlineStr"/>
       <c r="AN12" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO12" s="8" t="inlineStr"/>
@@ -13711,10 +13711,10 @@
         <v>46170.83333333334</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>46171.42708333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="AF13" s="8" t="n">
-        <v>4496.39</v>
+        <v>4432.15</v>
       </c>
       <c r="AG13" s="8" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>4432.15</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>64.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="8" t="inlineStr"/>
       <c r="AK13" s="8" t="inlineStr"/>
@@ -13733,7 +13733,7 @@
       <c r="AM13" s="8" t="inlineStr"/>
       <c r="AN13" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO13" s="8" t="inlineStr"/>
@@ -13802,10 +13802,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG14" s="8" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI14" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="8" t="inlineStr"/>
       <c r="AK14" s="8" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       <c r="AM14" s="8" t="inlineStr"/>
       <c r="AN14" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO14" s="8" t="inlineStr"/>
@@ -13893,10 +13893,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF15" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG15" s="8" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI15" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="8" t="inlineStr"/>
       <c r="AK15" s="8" t="inlineStr"/>
@@ -13915,7 +13915,7 @@
       <c r="AM15" s="8" t="inlineStr"/>
       <c r="AN15" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO15" s="8" t="inlineStr"/>
@@ -13984,10 +13984,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI16" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="8" t="inlineStr"/>
       <c r="AK16" s="8" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       <c r="AM16" s="8" t="inlineStr"/>
       <c r="AN16" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO16" s="8" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         <v>46171.42708333334</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>46171.5</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>4514.22</v>
+        <v>4496.39</v>
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>4496.39</v>
       </c>
       <c r="AI17" s="8" t="n">
-        <v>-17.83</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="8" t="inlineStr"/>
       <c r="AK17" s="8" t="inlineStr"/>
@@ -14097,7 +14097,7 @@
       <c r="AM17" s="8" t="inlineStr"/>
       <c r="AN17" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO17" s="8" t="inlineStr"/>
@@ -14530,10 +14530,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE22" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF22" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG22" s="8" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI22" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="8" t="inlineStr"/>
       <c r="AK22" s="8" t="inlineStr"/>
@@ -14552,7 +14552,7 @@
       <c r="AM22" s="8" t="inlineStr"/>
       <c r="AN22" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO22" s="8" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE23" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG23" s="8" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI23" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ23" s="8" t="inlineStr"/>
       <c r="AK23" s="8" t="inlineStr"/>
@@ -14643,7 +14643,7 @@
       <c r="AM23" s="8" t="inlineStr"/>
       <c r="AN23" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO23" s="8" t="inlineStr"/>
@@ -14712,10 +14712,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE24" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG24" s="8" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI24" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="8" t="inlineStr"/>
       <c r="AK24" s="8" t="inlineStr"/>
@@ -14734,7 +14734,7 @@
       <c r="AM24" s="8" t="inlineStr"/>
       <c r="AN24" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO24" s="8" t="inlineStr"/>
@@ -14803,10 +14803,10 @@
         <v>46171.82291666666</v>
       </c>
       <c r="AE25" s="9" t="n">
-        <v>46171.86458333334</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>4533.11</v>
+        <v>4514.17</v>
       </c>
       <c r="AG25" s="8" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>4514.17</v>
       </c>
       <c r="AI25" s="8" t="n">
-        <v>-18.94</v>
+        <v>0</v>
       </c>
       <c r="AJ25" s="8" t="inlineStr"/>
       <c r="AK25" s="8" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
       <c r="AM25" s="8" t="inlineStr"/>
       <c r="AN25" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO25" s="8" t="inlineStr"/>
@@ -15258,10 +15258,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE30" s="9" t="n">
-        <v>46172.07291666666</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF30" s="8" t="n">
-        <v>4552.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG30" s="8" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI30" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="8" t="inlineStr"/>
       <c r="AK30" s="8" t="inlineStr"/>
@@ -15280,7 +15280,7 @@
       <c r="AM30" s="8" t="inlineStr"/>
       <c r="AN30" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO30" s="8" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE31" s="9" t="n">
-        <v>46172.07291666666</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF31" s="8" t="n">
-        <v>4551.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG31" s="8" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI31" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="8" t="inlineStr"/>
       <c r="AK31" s="8" t="inlineStr"/>
@@ -15371,7 +15371,7 @@
       <c r="AM31" s="8" t="inlineStr"/>
       <c r="AN31" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO31" s="8" t="inlineStr"/>
@@ -15440,10 +15440,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE32" s="9" t="n">
-        <v>46172.11458333334</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF32" s="8" t="n">
-        <v>4548.14</v>
+        <v>4554.13</v>
       </c>
       <c r="AG32" s="8" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI32" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="8" t="inlineStr"/>
       <c r="AK32" s="8" t="inlineStr"/>
@@ -15462,7 +15462,7 @@
       <c r="AM32" s="8" t="inlineStr"/>
       <c r="AN32" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO32" s="8" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         <v>46172.03125</v>
       </c>
       <c r="AE33" s="9" t="n">
-        <v>46174.84375</v>
+        <v>46172.03125</v>
       </c>
       <c r="AF33" s="8" t="n">
-        <v>4470.65</v>
+        <v>4554.13</v>
       </c>
       <c r="AG33" s="8" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>4554.13</v>
       </c>
       <c r="AI33" s="8" t="n">
-        <v>83.48</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="8" t="inlineStr"/>
       <c r="AK33" s="8" t="inlineStr"/>
@@ -15553,7 +15553,7 @@
       <c r="AM33" s="8" t="inlineStr"/>
       <c r="AN33" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO33" s="8" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         <v>46175</v>
       </c>
       <c r="AE34" s="9" t="n">
-        <v>46175.01041666666</v>
+        <v>46175</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>4482.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG34" s="8" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI34" s="8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AJ34" s="8" t="inlineStr"/>
       <c r="AK34" s="8" t="inlineStr"/>
@@ -15644,7 +15644,7 @@
       <c r="AM34" s="8" t="inlineStr"/>
       <c r="AN34" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO34" s="8" t="inlineStr"/>
@@ -15713,10 +15713,10 @@
         <v>46175</v>
       </c>
       <c r="AE35" s="9" t="n">
-        <v>46175.02083333334</v>
+        <v>46175</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>4483.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG35" s="8" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI35" s="8" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="8" t="inlineStr"/>
       <c r="AK35" s="8" t="inlineStr"/>
@@ -15735,7 +15735,7 @@
       <c r="AM35" s="8" t="inlineStr"/>
       <c r="AN35" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO35" s="8" t="inlineStr"/>
@@ -15804,10 +15804,10 @@
         <v>46175</v>
       </c>
       <c r="AE36" s="9" t="n">
-        <v>46175.02083333334</v>
+        <v>46175</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>4486.1</v>
+        <v>4480.07</v>
       </c>
       <c r="AG36" s="8" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI36" s="8" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="8" t="inlineStr"/>
       <c r="AK36" s="8" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
       <c r="AM36" s="8" t="inlineStr"/>
       <c r="AN36" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO36" s="8" t="inlineStr"/>
@@ -15895,10 +15895,10 @@
         <v>46175</v>
       </c>
       <c r="AE37" s="9" t="n">
-        <v>46175.36458333334</v>
+        <v>46175</v>
       </c>
       <c r="AF37" s="8" t="n">
-        <v>4479.85</v>
+        <v>4480.07</v>
       </c>
       <c r="AG37" s="8" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>4480.07</v>
       </c>
       <c r="AI37" s="8" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="8" t="inlineStr"/>
       <c r="AK37" s="8" t="inlineStr"/>
@@ -15917,7 +15917,7 @@
       <c r="AM37" s="8" t="inlineStr"/>
       <c r="AN37" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO37" s="8" t="inlineStr"/>
@@ -15986,10 +15986,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE38" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>4477.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG38" s="8" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI38" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="8" t="inlineStr"/>
       <c r="AK38" s="8" t="inlineStr"/>
@@ -16008,7 +16008,7 @@
       <c r="AM38" s="8" t="inlineStr"/>
       <c r="AN38" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO38" s="8" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE39" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF39" s="8" t="n">
-        <v>4476.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG39" s="8" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI39" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ39" s="8" t="inlineStr"/>
       <c r="AK39" s="8" t="inlineStr"/>
@@ -16099,7 +16099,7 @@
       <c r="AM39" s="8" t="inlineStr"/>
       <c r="AN39" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO39" s="8" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE40" s="9" t="n">
-        <v>46175.375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF40" s="8" t="n">
-        <v>4473.86</v>
+        <v>4479.85</v>
       </c>
       <c r="AG40" s="8" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI40" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ40" s="8" t="inlineStr"/>
       <c r="AK40" s="8" t="inlineStr"/>
@@ -16190,7 +16190,7 @@
       <c r="AM40" s="8" t="inlineStr"/>
       <c r="AN40" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO40" s="8" t="inlineStr"/>
@@ -16259,10 +16259,10 @@
         <v>46175.36458333334</v>
       </c>
       <c r="AE41" s="9" t="n">
-        <v>46175.4375</v>
+        <v>46175.36458333334</v>
       </c>
       <c r="AF41" s="8" t="n">
-        <v>4495.18</v>
+        <v>4479.85</v>
       </c>
       <c r="AG41" s="8" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>4479.85</v>
       </c>
       <c r="AI41" s="8" t="n">
-        <v>-15.33</v>
+        <v>0</v>
       </c>
       <c r="AJ41" s="8" t="inlineStr"/>
       <c r="AK41" s="8" t="inlineStr"/>
@@ -16281,7 +16281,7 @@
       <c r="AM41" s="8" t="inlineStr"/>
       <c r="AN41" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO41" s="8" t="inlineStr"/>
@@ -16714,10 +16714,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE46" s="9" t="n">
-        <v>46175.84375</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF46" s="8" t="n">
-        <v>4512.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG46" s="8" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI46" s="8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AJ46" s="8" t="inlineStr"/>
       <c r="AK46" s="8" t="inlineStr"/>
@@ -16736,7 +16736,7 @@
       <c r="AM46" s="8" t="inlineStr"/>
       <c r="AN46" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO46" s="8" t="inlineStr"/>
@@ -16805,10 +16805,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE47" s="9" t="n">
-        <v>46175.84375</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF47" s="8" t="n">
-        <v>4511.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG47" s="8" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI47" s="8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AJ47" s="8" t="inlineStr"/>
       <c r="AK47" s="8" t="inlineStr"/>
@@ -16827,7 +16827,7 @@
       <c r="AM47" s="8" t="inlineStr"/>
       <c r="AN47" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO47" s="8" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE48" s="9" t="n">
-        <v>46175.85416666666</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF48" s="8" t="n">
-        <v>4508.22</v>
+        <v>4514.66</v>
       </c>
       <c r="AG48" s="8" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI48" s="8" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="AJ48" s="8" t="inlineStr"/>
       <c r="AK48" s="8" t="inlineStr"/>
@@ -16918,7 +16918,7 @@
       <c r="AM48" s="8" t="inlineStr"/>
       <c r="AN48" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO48" s="8" t="inlineStr"/>
@@ -16987,10 +16987,10 @@
         <v>46175.83333333334</v>
       </c>
       <c r="AE49" s="9" t="n">
-        <v>46176.3125</v>
+        <v>46175.83333333334</v>
       </c>
       <c r="AF49" s="8" t="n">
-        <v>4483.45</v>
+        <v>4514.66</v>
       </c>
       <c r="AG49" s="8" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>4514.66</v>
       </c>
       <c r="AI49" s="8" t="n">
-        <v>31.21</v>
+        <v>0</v>
       </c>
       <c r="AJ49" s="8" t="inlineStr"/>
       <c r="AK49" s="8" t="inlineStr"/>
@@ -17009,7 +17009,7 @@
       <c r="AM49" s="8" t="inlineStr"/>
       <c r="AN49" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO49" s="8" t="inlineStr"/>
@@ -17078,10 +17078,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE50" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF50" s="8" t="n">
-        <v>4485.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG50" s="8" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI50" s="8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="8" t="inlineStr"/>
       <c r="AK50" s="8" t="inlineStr"/>
@@ -17100,7 +17100,7 @@
       <c r="AM50" s="8" t="inlineStr"/>
       <c r="AN50" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO50" s="8" t="inlineStr"/>
@@ -17169,10 +17169,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE51" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF51" s="8" t="n">
-        <v>4486.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG51" s="8" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI51" s="8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="8" t="inlineStr"/>
       <c r="AK51" s="8" t="inlineStr"/>
@@ -17191,7 +17191,7 @@
       <c r="AM51" s="8" t="inlineStr"/>
       <c r="AN51" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO51" s="8" t="inlineStr"/>
@@ -17260,10 +17260,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE52" s="9" t="n">
-        <v>46176.32291666666</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF52" s="8" t="n">
-        <v>4489.18</v>
+        <v>4483.45</v>
       </c>
       <c r="AG52" s="8" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI52" s="8" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="8" t="inlineStr"/>
       <c r="AK52" s="8" t="inlineStr"/>
@@ -17282,7 +17282,7 @@
       <c r="AM52" s="8" t="inlineStr"/>
       <c r="AN52" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO52" s="8" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         <v>46176.3125</v>
       </c>
       <c r="AE53" s="9" t="n">
-        <v>46176.34375</v>
+        <v>46176.3125</v>
       </c>
       <c r="AF53" s="8" t="n">
-        <v>4471.34</v>
+        <v>4483.45</v>
       </c>
       <c r="AG53" s="8" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>4483.45</v>
       </c>
       <c r="AI53" s="8" t="n">
-        <v>-12.11</v>
+        <v>0</v>
       </c>
       <c r="AJ53" s="8" t="inlineStr"/>
       <c r="AK53" s="8" t="inlineStr"/>
@@ -17373,7 +17373,7 @@
       <c r="AM53" s="8" t="inlineStr"/>
       <c r="AN53" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO53" s="8" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE62" s="9" t="n">
-        <v>46176.51041666666</v>
+        <v>46176.5</v>
       </c>
       <c r="AF62" s="8" t="n">
-        <v>4467.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG62" s="8" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI62" s="8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AJ62" s="8" t="inlineStr"/>
       <c r="AK62" s="8" t="inlineStr"/>
@@ -18192,7 +18192,7 @@
       <c r="AM62" s="8" t="inlineStr"/>
       <c r="AN62" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO62" s="8" t="inlineStr"/>
@@ -18261,10 +18261,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE63" s="9" t="n">
-        <v>46176.51041666666</v>
+        <v>46176.5</v>
       </c>
       <c r="AF63" s="8" t="n">
-        <v>4466.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG63" s="8" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI63" s="8" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AJ63" s="8" t="inlineStr"/>
       <c r="AK63" s="8" t="inlineStr"/>
@@ -18283,7 +18283,7 @@
       <c r="AM63" s="8" t="inlineStr"/>
       <c r="AN63" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO63" s="8" t="inlineStr"/>
@@ -18352,10 +18352,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE64" s="9" t="n">
-        <v>46176.52083333334</v>
+        <v>46176.5</v>
       </c>
       <c r="AF64" s="8" t="n">
-        <v>4463.5</v>
+        <v>4469.51</v>
       </c>
       <c r="AG64" s="8" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI64" s="8" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AJ64" s="8" t="inlineStr"/>
       <c r="AK64" s="8" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       <c r="AM64" s="8" t="inlineStr"/>
       <c r="AN64" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO64" s="8" t="inlineStr"/>
@@ -18443,10 +18443,10 @@
         <v>46176.5</v>
       </c>
       <c r="AE65" s="9" t="n">
-        <v>46176.71875</v>
+        <v>46176.5</v>
       </c>
       <c r="AF65" s="8" t="n">
-        <v>4463.07</v>
+        <v>4469.51</v>
       </c>
       <c r="AG65" s="8" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>4469.51</v>
       </c>
       <c r="AI65" s="8" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="AJ65" s="8" t="inlineStr"/>
       <c r="AK65" s="8" t="inlineStr"/>
@@ -18465,7 +18465,7 @@
       <c r="AM65" s="8" t="inlineStr"/>
       <c r="AN65" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO65" s="8" t="inlineStr"/>
@@ -18534,10 +18534,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE66" s="9" t="n">
-        <v>46176.75</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF66" s="8" t="n">
-        <v>4465.06</v>
+        <v>4463.07</v>
       </c>
       <c r="AG66" s="8" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI66" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ66" s="8" t="inlineStr"/>
       <c r="AK66" s="8" t="inlineStr"/>
@@ -18556,7 +18556,7 @@
       <c r="AM66" s="8" t="inlineStr"/>
       <c r="AN66" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO66" s="8" t="inlineStr"/>
@@ -18625,10 +18625,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE67" s="9" t="n">
-        <v>46176.75</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF67" s="8" t="n">
-        <v>4466.06</v>
+        <v>4463.07</v>
       </c>
       <c r="AG67" s="8" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI67" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ67" s="8" t="inlineStr"/>
       <c r="AK67" s="8" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       <c r="AM67" s="8" t="inlineStr"/>
       <c r="AN67" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO67" s="8" t="inlineStr"/>
@@ -18716,10 +18716,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE68" s="9" t="n">
-        <v>46176.86458333334</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF68" s="8" t="n">
-        <v>4427.32</v>
+        <v>4463.07</v>
       </c>
       <c r="AG68" s="8" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI68" s="8" t="n">
-        <v>-35.75</v>
+        <v>0</v>
       </c>
       <c r="AJ68" s="8" t="inlineStr"/>
       <c r="AK68" s="8" t="inlineStr"/>
@@ -18738,7 +18738,7 @@
       <c r="AM68" s="8" t="inlineStr"/>
       <c r="AN68" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO68" s="8" t="inlineStr"/>
@@ -18807,10 +18807,10 @@
         <v>46176.71875</v>
       </c>
       <c r="AE69" s="9" t="n">
-        <v>46176.86458333334</v>
+        <v>46176.71875</v>
       </c>
       <c r="AF69" s="8" t="n">
-        <v>4427.32</v>
+        <v>4463.07</v>
       </c>
       <c r="AG69" s="8" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>4463.07</v>
       </c>
       <c r="AI69" s="8" t="n">
-        <v>-35.75</v>
+        <v>0</v>
       </c>
       <c r="AJ69" s="8" t="inlineStr"/>
       <c r="AK69" s="8" t="inlineStr"/>
@@ -18829,7 +18829,7 @@
       <c r="AM69" s="8" t="inlineStr"/>
       <c r="AN69" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO69" s="8" t="inlineStr"/>
@@ -19262,10 +19262,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE74" s="9" t="n">
-        <v>46176.90625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF74" s="8" t="n">
-        <v>4456.54</v>
+        <v>4454.76</v>
       </c>
       <c r="AG74" s="8" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI74" s="8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AJ74" s="8" t="inlineStr"/>
       <c r="AK74" s="8" t="inlineStr"/>
@@ -19284,7 +19284,7 @@
       <c r="AM74" s="8" t="inlineStr"/>
       <c r="AN74" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO74" s="8" t="inlineStr"/>
@@ -19353,10 +19353,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE75" s="9" t="n">
-        <v>46176.90625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF75" s="8" t="n">
-        <v>4457.54</v>
+        <v>4454.76</v>
       </c>
       <c r="AG75" s="8" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI75" s="8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AJ75" s="8" t="inlineStr"/>
       <c r="AK75" s="8" t="inlineStr"/>
@@ -19375,7 +19375,7 @@
       <c r="AM75" s="8" t="inlineStr"/>
       <c r="AN75" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO75" s="8" t="inlineStr"/>
@@ -19444,10 +19444,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE76" s="9" t="n">
-        <v>46177.15625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF76" s="8" t="n">
-        <v>4433.48</v>
+        <v>4454.76</v>
       </c>
       <c r="AG76" s="8" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI76" s="8" t="n">
-        <v>-21.28</v>
+        <v>0</v>
       </c>
       <c r="AJ76" s="8" t="inlineStr"/>
       <c r="AK76" s="8" t="inlineStr"/>
@@ -19466,7 +19466,7 @@
       <c r="AM76" s="8" t="inlineStr"/>
       <c r="AN76" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO76" s="8" t="inlineStr"/>
@@ -19535,10 +19535,10 @@
         <v>46176.88541666666</v>
       </c>
       <c r="AE77" s="9" t="n">
-        <v>46177.15625</v>
+        <v>46176.88541666666</v>
       </c>
       <c r="AF77" s="8" t="n">
-        <v>4433.48</v>
+        <v>4454.76</v>
       </c>
       <c r="AG77" s="8" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>4454.76</v>
       </c>
       <c r="AI77" s="8" t="n">
-        <v>-21.28</v>
+        <v>0</v>
       </c>
       <c r="AJ77" s="8" t="inlineStr"/>
       <c r="AK77" s="8" t="inlineStr"/>
@@ -19557,7 +19557,7 @@
       <c r="AM77" s="8" t="inlineStr"/>
       <c r="AN77" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO77" s="8" t="inlineStr"/>
@@ -19626,10 +19626,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE78" s="9" t="n">
-        <v>46177.20833333334</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF78" s="8" t="n">
-        <v>4431.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG78" s="8" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI78" s="8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ78" s="8" t="inlineStr"/>
       <c r="AK78" s="8" t="inlineStr"/>
@@ -19648,7 +19648,7 @@
       <c r="AM78" s="8" t="inlineStr"/>
       <c r="AN78" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO78" s="8" t="inlineStr"/>
@@ -19717,10 +19717,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE79" s="9" t="n">
-        <v>46177.20833333334</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF79" s="8" t="n">
-        <v>4430.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG79" s="8" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI79" s="8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ79" s="8" t="inlineStr"/>
       <c r="AK79" s="8" t="inlineStr"/>
@@ -19739,7 +19739,7 @@
       <c r="AM79" s="8" t="inlineStr"/>
       <c r="AN79" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO79" s="8" t="inlineStr"/>
@@ -19808,10 +19808,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE80" s="9" t="n">
-        <v>46177.21875</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF80" s="8" t="n">
-        <v>4427.55</v>
+        <v>4433.48</v>
       </c>
       <c r="AG80" s="8" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI80" s="8" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="AJ80" s="8" t="inlineStr"/>
       <c r="AK80" s="8" t="inlineStr"/>
@@ -19830,7 +19830,7 @@
       <c r="AM80" s="8" t="inlineStr"/>
       <c r="AN80" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO80" s="8" t="inlineStr"/>
@@ -19899,10 +19899,10 @@
         <v>46177.15625</v>
       </c>
       <c r="AE81" s="9" t="n">
-        <v>46177.25</v>
+        <v>46177.15625</v>
       </c>
       <c r="AF81" s="8" t="n">
-        <v>4449.14</v>
+        <v>4433.48</v>
       </c>
       <c r="AG81" s="8" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>4433.48</v>
       </c>
       <c r="AI81" s="8" t="n">
-        <v>-15.66</v>
+        <v>0</v>
       </c>
       <c r="AJ81" s="8" t="inlineStr"/>
       <c r="AK81" s="8" t="inlineStr"/>
@@ -19921,7 +19921,7 @@
       <c r="AM81" s="8" t="inlineStr"/>
       <c r="AN81" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO81" s="8" t="inlineStr"/>
@@ -20354,10 +20354,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE86" s="9" t="n">
-        <v>46177.60416666666</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF86" s="8" t="n">
-        <v>4462.16</v>
+        <v>4464.11</v>
       </c>
       <c r="AG86" s="8" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI86" s="8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ86" s="8" t="inlineStr"/>
       <c r="AK86" s="8" t="inlineStr"/>
@@ -20376,7 +20376,7 @@
       <c r="AM86" s="8" t="inlineStr"/>
       <c r="AN86" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO86" s="8" t="inlineStr"/>
@@ -20445,10 +20445,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE87" s="9" t="n">
-        <v>46177.60416666666</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF87" s="8" t="n">
-        <v>4461.16</v>
+        <v>4464.11</v>
       </c>
       <c r="AG87" s="8" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI87" s="8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AJ87" s="8" t="inlineStr"/>
       <c r="AK87" s="8" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       <c r="AM87" s="8" t="inlineStr"/>
       <c r="AN87" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO87" s="8" t="inlineStr"/>
@@ -20536,10 +20536,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE88" s="9" t="n">
-        <v>46177.77083333334</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF88" s="8" t="n">
-        <v>4489.65</v>
+        <v>4464.11</v>
       </c>
       <c r="AG88" s="8" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI88" s="8" t="n">
-        <v>-25.54</v>
+        <v>0</v>
       </c>
       <c r="AJ88" s="8" t="inlineStr"/>
       <c r="AK88" s="8" t="inlineStr"/>
@@ -20558,7 +20558,7 @@
       <c r="AM88" s="8" t="inlineStr"/>
       <c r="AN88" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO88" s="8" t="inlineStr"/>
@@ -20627,10 +20627,10 @@
         <v>46177.59375</v>
       </c>
       <c r="AE89" s="9" t="n">
-        <v>46177.77083333334</v>
+        <v>46177.59375</v>
       </c>
       <c r="AF89" s="8" t="n">
-        <v>4489.65</v>
+        <v>4464.11</v>
       </c>
       <c r="AG89" s="8" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>4464.11</v>
       </c>
       <c r="AI89" s="8" t="n">
-        <v>-25.54</v>
+        <v>0</v>
       </c>
       <c r="AJ89" s="8" t="inlineStr"/>
       <c r="AK89" s="8" t="inlineStr"/>
@@ -20649,7 +20649,7 @@
       <c r="AM89" s="8" t="inlineStr"/>
       <c r="AN89" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO89" s="8" t="inlineStr"/>
@@ -21082,10 +21082,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE94" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF94" s="8" t="n">
-        <v>4485.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG94" s="8" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI94" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ94" s="8" t="inlineStr"/>
       <c r="AK94" s="8" t="inlineStr"/>
@@ -21104,7 +21104,7 @@
       <c r="AM94" s="8" t="inlineStr"/>
       <c r="AN94" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO94" s="8" t="inlineStr"/>
@@ -21173,10 +21173,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE95" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF95" s="8" t="n">
-        <v>4484.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG95" s="8" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI95" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ95" s="8" t="inlineStr"/>
       <c r="AK95" s="8" t="inlineStr"/>
@@ -21195,7 +21195,7 @@
       <c r="AM95" s="8" t="inlineStr"/>
       <c r="AN95" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO95" s="8" t="inlineStr"/>
@@ -21264,10 +21264,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE96" s="9" t="n">
-        <v>46177.89583333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF96" s="8" t="n">
-        <v>4481.83</v>
+        <v>4487.82</v>
       </c>
       <c r="AG96" s="8" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI96" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ96" s="8" t="inlineStr"/>
       <c r="AK96" s="8" t="inlineStr"/>
@@ -21286,7 +21286,7 @@
       <c r="AM96" s="8" t="inlineStr"/>
       <c r="AN96" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO96" s="8" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         <v>46177.88541666666</v>
       </c>
       <c r="AE97" s="9" t="n">
-        <v>46178.58333333334</v>
+        <v>46177.88541666666</v>
       </c>
       <c r="AF97" s="8" t="n">
-        <v>4452.87</v>
+        <v>4487.82</v>
       </c>
       <c r="AG97" s="8" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>4487.82</v>
       </c>
       <c r="AI97" s="8" t="n">
-        <v>34.95</v>
+        <v>0</v>
       </c>
       <c r="AJ97" s="8" t="inlineStr"/>
       <c r="AK97" s="8" t="inlineStr"/>
@@ -21377,7 +21377,7 @@
       <c r="AM97" s="8" t="inlineStr"/>
       <c r="AN97" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO97" s="8" t="inlineStr"/>
@@ -21446,10 +21446,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE98" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF98" s="8" t="n">
-        <v>4454.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG98" s="8" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI98" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AJ98" s="8" t="inlineStr"/>
       <c r="AK98" s="8" t="inlineStr"/>
@@ -21468,7 +21468,7 @@
       <c r="AM98" s="8" t="inlineStr"/>
       <c r="AN98" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO98" s="8" t="inlineStr"/>
@@ -21537,10 +21537,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE99" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF99" s="8" t="n">
-        <v>4455.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG99" s="8" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI99" s="8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AJ99" s="8" t="inlineStr"/>
       <c r="AK99" s="8" t="inlineStr"/>
@@ -21559,7 +21559,7 @@
       <c r="AM99" s="8" t="inlineStr"/>
       <c r="AN99" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO99" s="8" t="inlineStr"/>
@@ -21628,10 +21628,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE100" s="9" t="n">
-        <v>46178.59375</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF100" s="8" t="n">
-        <v>4458.86</v>
+        <v>4452.87</v>
       </c>
       <c r="AG100" s="8" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI100" s="8" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="AJ100" s="8" t="inlineStr"/>
       <c r="AK100" s="8" t="inlineStr"/>
@@ -21650,7 +21650,7 @@
       <c r="AM100" s="8" t="inlineStr"/>
       <c r="AN100" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO100" s="8" t="inlineStr"/>
@@ -21719,10 +21719,10 @@
         <v>46178.58333333334</v>
       </c>
       <c r="AE101" s="9" t="n">
-        <v>46178.82291666666</v>
+        <v>46178.58333333334</v>
       </c>
       <c r="AF101" s="8" t="n">
-        <v>4413.06</v>
+        <v>4452.87</v>
       </c>
       <c r="AG101" s="8" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>4452.87</v>
       </c>
       <c r="AI101" s="8" t="n">
-        <v>-39.81</v>
+        <v>0</v>
       </c>
       <c r="AJ101" s="8" t="inlineStr"/>
       <c r="AK101" s="8" t="inlineStr"/>
@@ -21741,7 +21741,7 @@
       <c r="AM101" s="8" t="inlineStr"/>
       <c r="AN101" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO101" s="8" t="inlineStr"/>
@@ -22174,10 +22174,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE106" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF106" s="8" t="n">
-        <v>4340.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG106" s="8" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI106" s="8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AJ106" s="8" t="inlineStr"/>
       <c r="AK106" s="8" t="inlineStr"/>
@@ -22196,7 +22196,7 @@
       <c r="AM106" s="8" t="inlineStr"/>
       <c r="AN106" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO106" s="8" t="inlineStr"/>
@@ -22265,10 +22265,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE107" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF107" s="8" t="n">
-        <v>4341.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG107" s="8" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI107" s="8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AJ107" s="8" t="inlineStr"/>
       <c r="AK107" s="8" t="inlineStr"/>
@@ -22287,7 +22287,7 @@
       <c r="AM107" s="8" t="inlineStr"/>
       <c r="AN107" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO107" s="8" t="inlineStr"/>
@@ -22356,10 +22356,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE108" s="9" t="n">
-        <v>46181.29166666666</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF108" s="8" t="n">
-        <v>4344.95</v>
+        <v>4338.98</v>
       </c>
       <c r="AG108" s="8" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI108" s="8" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AJ108" s="8" t="inlineStr"/>
       <c r="AK108" s="8" t="inlineStr"/>
@@ -22378,7 +22378,7 @@
       <c r="AM108" s="8" t="inlineStr"/>
       <c r="AN108" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO108" s="8" t="inlineStr"/>
@@ -22447,10 +22447,10 @@
         <v>46181.28125</v>
       </c>
       <c r="AE109" s="9" t="n">
-        <v>46181.34375</v>
+        <v>46181.28125</v>
       </c>
       <c r="AF109" s="8" t="n">
-        <v>4326.96</v>
+        <v>4338.98</v>
       </c>
       <c r="AG109" s="8" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>4338.98</v>
       </c>
       <c r="AI109" s="8" t="n">
-        <v>-12.02</v>
+        <v>0</v>
       </c>
       <c r="AJ109" s="8" t="inlineStr"/>
       <c r="AK109" s="8" t="inlineStr"/>
@@ -22469,7 +22469,7 @@
       <c r="AM109" s="8" t="inlineStr"/>
       <c r="AN109" s="8" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="AO109" s="8" t="inlineStr"/>
@@ -23334,7 +23334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -23391,25 +23391,25 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>128.26</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>46181.28125</v>
+        <v>46177.88541666666</v>
       </c>
     </row>
     <row r="3">
@@ -23420,25 +23420,25 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TREND_RECHECK</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>274.36</v>
+        <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>46170.75</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>46181.34375</v>
+        <v>46181.28125</v>
       </c>
     </row>
     <row r="4">
@@ -23449,25 +23449,25 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-259.78</v>
+        <v>53.62</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>46171.42708333334</v>
+        <v>46171.5</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>46181.34375</v>
+        <v>46177.77083333334</v>
       </c>
     </row>
     <row r="5">
@@ -23478,25 +23478,25 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>S13_FLIP</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-99.59999999999999</v>
+        <v>118.93</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46170.75</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>46181.28125</v>
+        <v>46181.34375</v>
       </c>
     </row>
     <row r="6">
@@ -23507,25 +23507,25 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>S13_FLIP</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-88.90000000000001</v>
+        <v>-15.81</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>46170.75</v>
+        <v>46171.5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>46170.75</v>
+        <v>46177.77083333334</v>
       </c>
     </row>
     <row r="7">
@@ -23536,65 +23536,65 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>S13_FLIP</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-39.81</v>
+        <v>-103.23</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>46178.58333333334</v>
+        <v>46176.34375</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>46178.58333333334</v>
+        <v>46181.34375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>bt</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-85.47</v>
+        <v>-88.90000000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>46170.60416666666</v>
+        <v>46170.75</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>46181.34375</v>
+        <v>46170.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>bt_s14_family</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>NO_SAME_SIDE_CANDIDATE</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -23603,16 +23603,16 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-11.15</v>
+        <v>-35.39</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>46170.60416666666</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>46181.28125</v>
+        <v>46181.34375</v>
       </c>
     </row>
     <row r="10">
@@ -23628,24 +23628,53 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-74.31999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="F10" s="11" t="n">
+        <v>46170.60416666666</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>46181.28125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>bt_s14_family</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-73.2</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>46170.75</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G11" s="11" t="n">
         <v>46181.34375</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel_reports/backtest_compare/s13/compare_s13_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s13/compare_s13_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:39:19</t>
+          <t>2026-06-19 17:10:00</t>
         </is>
       </c>
     </row>
@@ -23334,10 +23334,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -23615,66 +23615,8 @@
         <v>46181.34375</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>46170.60416666666</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>46181.28125</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>-73.2</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>46170.75</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>46181.34375</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>